--- a/health_coach_forms/014_health_belief_model_questionnaire--health_coach_forms.xlsx
+++ b/health_coach_forms/014_health_belief_model_questionnaire--health_coach_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,23 +515,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>patient_beliefs</t>
+          <t>health_belief_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Patient Beliefs</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What motivates you to adopt healthy habits?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,110 +547,130 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>disease_beliefs</t>
+          <t>health_practice_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Disease Beliefs</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How often do you exercise?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please enter a number.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>health_change_label</t>
+          <t>disease_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Health Change</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Do you have any chronic health conditions?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>health_change_2_label</t>
+          <t>health_change_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>health_change_2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How often do you see a doctor or healthcare professional?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please enter a number.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>health_change_3_label</t>
+          <t>health_practice_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>health_change_3</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What are some of the most important factors that influence your health choices?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>disease_label</t>
+          <t>disease_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Disease</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What are some of the most significant health risks you face?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,64 +682,76 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>health_practice_label</t>
+          <t>health_practice_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Health Practice</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How often do you engage in activities that promote mental well-being?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter a number.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>health_change_label</t>
+          <t>disease_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Health Change</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Do you have any physical symptoms or health issues?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>health_change_4_label</t>
+          <t>health_practice_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>health_change_4</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What are some of the most significant health benefits you've experienced?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +763,49 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>health_change_2_label</t>
+          <t>disease_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>health_change_2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Do you have a plan for managing chronic health conditions?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>health_change_3_label</t>
+          <t>health_practice_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>health_change_3</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How often do you engage in activities that promote relaxation and stress reduction?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please enter a number.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +817,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>health_change_label</t>
+          <t>disease_5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>health_change</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What are some of the most significant health challenges you face?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,41 +844,49 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>disease_2_label</t>
+          <t>health_practice_6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>disease_2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Do you have a support system that helps you cope with stress?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>disease_3_label</t>
+          <t>disease_6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>disease_3</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>How often do you engage in activities that promote social connections?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please enter a number.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,64 +898,76 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>disease_4_label</t>
+          <t>health_practice_7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>disease_4</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>What are some of the most significant factors that influence your health choices?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>disease_label</t>
+          <t>disease_7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Disease</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Do you have any chronic health conditions or diseases?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>health_practice_2_label</t>
+          <t>health_practice_8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>health_practice_2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>What are some of the most significant barriers to your health and wellness?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,64 +979,76 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>health_practice_3_label</t>
+          <t>disease_8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>health_practice_3</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>How often do you engage in self-reflection and self-awareness?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please enter a number.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>health_practice_4_label</t>
+          <t>health_practice_9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>health_practice_4</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Health Practice 9</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>health_practice_5_label</t>
+          <t>disease_9</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>health_practice_5</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Do you have a plan for emergency situations?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Please select all that apply.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -980,110 +1060,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>disease_2</t>
+          <t>health_practice_10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Disease 2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Health Practice 10</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Please enter a number.</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>disease_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Disease 3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>disease_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Disease 4</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>disease_5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Disease 5</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>disease_6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Disease 6</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1090,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,850 +1118,1190 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>health_change_label_choices</t>
+          <t>health_belief_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>health_change_label_choices</t>
+          <t>health_belief_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>health_change_label_choices</t>
+          <t>health_belief_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree Nor Disagree'}</t>
+          <t>Neither Agree Nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>health_change_label_choices</t>
+          <t>health_belief_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>health_change_label_choices</t>
+          <t>health_belief_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>health_change_2_label_choices</t>
+          <t>disease_1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>health_change_2_label_choices</t>
+          <t>disease_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>health_change_2_label_choices</t>
+          <t>disease_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree Nor Disagree'}</t>
+          <t>Neither Agree Nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>health_change_2_label_choices</t>
+          <t>disease_1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>health_change_2_label_choices</t>
+          <t>disease_1_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>health_change_3_label_choices</t>
+          <t>health_practice_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>health_change_3_label_choices</t>
+          <t>health_practice_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>health_change_3_label_choices</t>
+          <t>health_practice_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree Nor Disagree'}</t>
+          <t>Neither Agree Nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>health_change_3_label_choices</t>
+          <t>health_practice_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>health_change_3_label_choices</t>
+          <t>health_practice_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>health_change_4_label_choices</t>
+          <t>disease_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>health_change_4_label_choices</t>
+          <t>disease_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>health_change_4_label_choices</t>
+          <t>disease_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree Nor Disagree'}</t>
+          <t>Neither Agree Nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>health_change_4_label_choices</t>
+          <t>disease_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>health_change_4_label_choices</t>
+          <t>disease_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>health_change_2_label_choices</t>
+          <t>disease_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>health_change_2_label_choices</t>
+          <t>disease_3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>health_change_2_label_choices</t>
+          <t>disease_3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree Nor Disagree'}</t>
+          <t>Neither Agree Nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>health_change_2_label_choices</t>
+          <t>disease_3_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>health_change_2_label_choices</t>
+          <t>disease_3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>health_change_3_label_choices</t>
+          <t>health_practice_4_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>health_change_3_label_choices</t>
+          <t>health_practice_4_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>health_change_3_label_choices</t>
+          <t>health_practice_4_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree Nor Disagree'}</t>
+          <t>Neither Agree Nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>health_change_3_label_choices</t>
+          <t>health_practice_4_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>health_change_3_label_choices</t>
+          <t>health_practice_4_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>health_change_label_choices</t>
+          <t>disease_4_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>health_change_label_choices</t>
+          <t>disease_4_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>health_change_label_choices</t>
+          <t>disease_4_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree Nor Disagree'}</t>
+          <t>Neither Agree Nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>health_change_label_choices</t>
+          <t>disease_4_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>health_change_label_choices</t>
+          <t>disease_4_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>disease_2_label_choices</t>
+          <t>disease_5_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>disease_2_label_choices</t>
+          <t>disease_5_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>disease_2_label_choices</t>
+          <t>disease_5_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree Nor Disagree'}</t>
+          <t>Neither Agree Nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>disease_2_label_choices</t>
+          <t>disease_5_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>disease_2_label_choices</t>
+          <t>disease_5_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>disease_3_label_choices</t>
+          <t>health_practice_6_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>disease_3_label_choices</t>
+          <t>health_practice_6_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>disease_3_label_choices</t>
+          <t>health_practice_6_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree Nor Disagree'}</t>
+          <t>Neither Agree Nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>disease_3_label_choices</t>
+          <t>health_practice_6_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>disease_3_label_choices</t>
+          <t>health_practice_6_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>disease_4_label_choices</t>
+          <t>health_practice_7_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>disease_4_label_choices</t>
+          <t>health_practice_7_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>disease_4_label_choices</t>
+          <t>health_practice_7_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree Nor Disagree'}</t>
+          <t>Neither Agree Nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>disease_4_label_choices</t>
+          <t>health_practice_7_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>disease_4_label_choices</t>
+          <t>health_practice_7_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease_7_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>strongly_agree</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Strongly Agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease_7_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>somewhat_agree</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Somewhat Agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease_7_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>neither_agree_nor_disagree</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Neither Agree Nor Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease_7_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>somewhat_disagree</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Somewhat Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease_7_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>strongly_disagree</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Strongly Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>health_practice_8_choices</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>strongly_agree</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Strongly Agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>health_practice_8_choices</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>somewhat_agree</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Somewhat Agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>health_practice_8_choices</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>neither_agree_nor_disagree</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Neither Agree Nor Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>health_practice_8_choices</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>somewhat_disagree</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Somewhat Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>health_practice_8_choices</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>strongly_disagree</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Strongly Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>health_practice_9_choices</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>strongly_agree</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Strongly Agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>health_practice_9_choices</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>somewhat_agree</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Somewhat Agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>health_practice_9_choices</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>neither_agree_nor_disagree</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Neither Agree Nor Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>health_practice_9_choices</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>somewhat_disagree</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Somewhat Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>health_practice_9_choices</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>strongly_disagree</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Strongly Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease_9_choices</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>strongly_agree</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Strongly Agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease_9_choices</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>somewhat_agree</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Somewhat Agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease_9_choices</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>neither_agree_nor_disagree</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Neither Agree Nor Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease_9_choices</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>somewhat_disagree</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Somewhat Disagree</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease_9_choices</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>strongly_disagree</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
